--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:21</t>
+    <t xml:space="preserve">2026-08-17 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:09</t>
+    <t xml:space="preserve">2026-08-17 20:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 20:26</t>
+    <t xml:space="preserve">2026-09-01 17:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:25</t>
+    <t xml:space="preserve">2026-09-06 21:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
